--- a/excel-files/PASIG/DELA PAZ ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASIG/DELA PAZ ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52BE3E1C-F7AA-4DC2-854F-E5329B383C95}"/>
+  <xr:revisionPtr revIDLastSave="385" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5EB4ED2-4D0C-4FE6-99C8-1DE6E46364C9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="95">
   <si>
     <t>Grade Level</t>
   </si>
@@ -3479,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3563,16 +3563,22 @@
       <c r="C3" s="1">
         <v>136</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
+      <c r="D3" s="1">
+        <v>190</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1">
@@ -3653,7 +3659,9 @@
       <c r="C6" s="1">
         <v>136</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
@@ -3680,7 +3688,9 @@
       <c r="C8" s="1">
         <v>162</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
@@ -3702,7 +3712,9 @@
       <c r="C9" s="1">
         <v>162</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
@@ -3724,7 +3736,9 @@
       <c r="C10" s="1">
         <v>162</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
@@ -3746,7 +3760,9 @@
       <c r="C11" s="1">
         <v>162</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
@@ -3768,7 +3784,9 @@
       <c r="C12" s="1">
         <v>162</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
@@ -3795,7 +3813,9 @@
       <c r="C14" s="1">
         <v>138</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
@@ -3817,7 +3837,9 @@
       <c r="C15" s="1">
         <v>138</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
@@ -3839,7 +3861,9 @@
       <c r="C16" s="1">
         <v>138</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
@@ -3861,7 +3885,9 @@
       <c r="C17" s="1">
         <v>138</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
@@ -3883,7 +3909,9 @@
       <c r="C18" s="1">
         <v>138</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
@@ -3905,7 +3933,9 @@
       <c r="C19" s="1">
         <v>138</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
@@ -4133,7 +4163,9 @@
       <c r="C28" s="1">
         <v>164</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
@@ -4155,7 +4187,9 @@
       <c r="C29" s="1">
         <v>164</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
       <c r="E29" s="1"/>
       <c r="F29" s="5"/>
       <c r="G29" s="3">
@@ -4187,16 +4221,22 @@
       <c r="C31" s="1">
         <v>167</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="1">
+        <v>232</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4209,7 +4249,9 @@
       <c r="C32" s="1">
         <v>167</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
@@ -4231,7 +4273,9 @@
       <c r="C33" s="1">
         <v>167</v>
       </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
@@ -4253,7 +4297,9 @@
       <c r="C34" s="1">
         <v>167</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
@@ -4276,7 +4322,7 @@
         <v>167</v>
       </c>
       <c r="D35" s="1">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="E35" s="1">
         <v>2025</v>
@@ -4286,11 +4332,11 @@
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4303,16 +4349,22 @@
       <c r="C36" s="1">
         <v>167</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="D36" s="1">
+        <v>232</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4325,7 +4377,9 @@
       <c r="C37" s="1">
         <v>167</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="5"/>
       <c r="G37" s="3">
@@ -4347,16 +4401,22 @@
       <c r="C38" s="1">
         <v>167</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>232</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4369,7 +4429,9 @@
       <c r="C39" s="1">
         <v>167</v>
       </c>
-      <c r="D39" s="1"/>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
@@ -4401,7 +4463,9 @@
       <c r="C41" s="1">
         <v>167</v>
       </c>
-      <c r="D41" s="1"/>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
@@ -4451,7 +4515,9 @@
       <c r="C43" s="1">
         <v>167</v>
       </c>
-      <c r="D43" s="1"/>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
@@ -4473,7 +4539,9 @@
       <c r="C44" s="1">
         <v>167</v>
       </c>
-      <c r="D44" s="1"/>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
@@ -4495,7 +4563,9 @@
       <c r="C45" s="1">
         <v>167</v>
       </c>
-      <c r="D45" s="1"/>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
@@ -4517,7 +4587,9 @@
       <c r="C46" s="1">
         <v>167</v>
       </c>
-      <c r="D46" s="1"/>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
@@ -4539,7 +4611,9 @@
       <c r="C47" s="1">
         <v>167</v>
       </c>
-      <c r="D47" s="1"/>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
@@ -4561,7 +4635,9 @@
       <c r="C48" s="1">
         <v>167</v>
       </c>
-      <c r="D48" s="1"/>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
@@ -4583,7 +4659,9 @@
       <c r="C49" s="1">
         <v>167</v>
       </c>
-      <c r="D49" s="1"/>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
@@ -4613,7 +4691,9 @@
         <v>18</v>
       </c>
       <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
       <c r="E51" s="10"/>
       <c r="F51" s="12"/>
       <c r="G51" s="3">
@@ -4633,7 +4713,9 @@
         <v>19</v>
       </c>
       <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
+      <c r="D52" s="10">
+        <v>0</v>
+      </c>
       <c r="E52" s="10"/>
       <c r="F52" s="12"/>
       <c r="G52" s="3">
@@ -4653,7 +4735,9 @@
         <v>16</v>
       </c>
       <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
+      <c r="D53" s="10">
+        <v>0</v>
+      </c>
       <c r="E53" s="10"/>
       <c r="F53" s="12"/>
       <c r="G53" s="3">
@@ -4673,7 +4757,9 @@
         <v>24</v>
       </c>
       <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="D54" s="10">
+        <v>0</v>
+      </c>
       <c r="E54" s="10"/>
       <c r="F54" s="12"/>
       <c r="G54" s="3">
@@ -4693,7 +4779,9 @@
         <v>20</v>
       </c>
       <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
       <c r="E55" s="10"/>
       <c r="F55" s="12"/>
       <c r="G55" s="3">
@@ -4713,7 +4801,9 @@
         <v>17</v>
       </c>
       <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="D56" s="10">
+        <v>0</v>
+      </c>
       <c r="E56" s="10"/>
       <c r="F56" s="12"/>
       <c r="G56" s="3">
@@ -4733,7 +4823,9 @@
         <v>21</v>
       </c>
       <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
+      <c r="D57" s="10">
+        <v>0</v>
+      </c>
       <c r="E57" s="10"/>
       <c r="F57" s="12"/>
       <c r="G57" s="3">
@@ -4753,7 +4845,9 @@
         <v>25</v>
       </c>
       <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
+      <c r="D58" s="10">
+        <v>0</v>
+      </c>
       <c r="E58" s="10"/>
       <c r="F58" s="12"/>
       <c r="G58" s="3">
@@ -4773,7 +4867,9 @@
         <v>23</v>
       </c>
       <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
+      <c r="D59" s="10">
+        <v>0</v>
+      </c>
       <c r="E59" s="10"/>
       <c r="F59" s="12"/>
       <c r="G59" s="3">
@@ -4803,7 +4899,9 @@
         <v>18</v>
       </c>
       <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
+      <c r="D61" s="10">
+        <v>0</v>
+      </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
@@ -4823,7 +4921,9 @@
         <v>19</v>
       </c>
       <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
+      <c r="D62" s="10">
+        <v>0</v>
+      </c>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
@@ -4843,7 +4943,9 @@
         <v>16</v>
       </c>
       <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="10">
+        <v>0</v>
+      </c>
       <c r="E63" s="10"/>
       <c r="F63" s="12"/>
       <c r="G63" s="3">
@@ -4863,7 +4965,9 @@
         <v>24</v>
       </c>
       <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="10">
+        <v>0</v>
+      </c>
       <c r="E64" s="10"/>
       <c r="F64" s="12"/>
       <c r="G64" s="3">
@@ -4883,7 +4987,9 @@
         <v>26</v>
       </c>
       <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
+      <c r="D65" s="10">
+        <v>0</v>
+      </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
       <c r="G65" s="3">
@@ -4903,7 +5009,9 @@
         <v>17</v>
       </c>
       <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="10">
+        <v>0</v>
+      </c>
       <c r="E66" s="10"/>
       <c r="F66" s="12"/>
       <c r="G66" s="3">
@@ -4923,7 +5031,9 @@
         <v>21</v>
       </c>
       <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="10">
+        <v>0</v>
+      </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
       <c r="G67" s="3">
@@ -4943,7 +5053,9 @@
         <v>25</v>
       </c>
       <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="10">
+        <v>0</v>
+      </c>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
       <c r="G68" s="3">
@@ -4963,7 +5075,9 @@
         <v>23</v>
       </c>
       <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="10">
+        <v>0</v>
+      </c>
       <c r="E69" s="10"/>
       <c r="F69" s="12"/>
       <c r="G69" s="3">
@@ -4993,7 +5107,9 @@
         <v>18</v>
       </c>
       <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
+      <c r="D71" s="10">
+        <v>0</v>
+      </c>
       <c r="E71" s="10"/>
       <c r="F71" s="12"/>
       <c r="G71" s="3">
@@ -5013,7 +5129,9 @@
         <v>19</v>
       </c>
       <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
+      <c r="D72" s="10">
+        <v>0</v>
+      </c>
       <c r="E72" s="10"/>
       <c r="F72" s="12"/>
       <c r="G72" s="3">
@@ -5033,7 +5151,9 @@
         <v>16</v>
       </c>
       <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
+      <c r="D73" s="10">
+        <v>0</v>
+      </c>
       <c r="E73" s="10"/>
       <c r="F73" s="12"/>
       <c r="G73" s="3">
@@ -5053,7 +5173,9 @@
         <v>24</v>
       </c>
       <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
+      <c r="D74" s="10">
+        <v>0</v>
+      </c>
       <c r="E74" s="10"/>
       <c r="F74" s="12"/>
       <c r="G74" s="3">
@@ -5073,7 +5195,9 @@
         <v>26</v>
       </c>
       <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
+      <c r="D75" s="10">
+        <v>0</v>
+      </c>
       <c r="E75" s="10"/>
       <c r="F75" s="12"/>
       <c r="G75" s="3">
@@ -5093,7 +5217,9 @@
         <v>17</v>
       </c>
       <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
+      <c r="D76" s="10">
+        <v>0</v>
+      </c>
       <c r="E76" s="10"/>
       <c r="F76" s="12"/>
       <c r="G76" s="3">
@@ -5113,7 +5239,9 @@
         <v>21</v>
       </c>
       <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
+      <c r="D77" s="10">
+        <v>0</v>
+      </c>
       <c r="E77" s="10"/>
       <c r="F77" s="12"/>
       <c r="G77" s="3">
@@ -5133,7 +5261,9 @@
         <v>25</v>
       </c>
       <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
+      <c r="D78" s="10">
+        <v>0</v>
+      </c>
       <c r="E78" s="10"/>
       <c r="F78" s="12"/>
       <c r="G78" s="3">
@@ -5153,7 +5283,9 @@
         <v>23</v>
       </c>
       <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
+      <c r="D79" s="10">
+        <v>0</v>
+      </c>
       <c r="E79" s="10"/>
       <c r="F79" s="12"/>
       <c r="G79" s="3">
@@ -5183,7 +5315,9 @@
         <v>18</v>
       </c>
       <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
+      <c r="D81" s="10">
+        <v>0</v>
+      </c>
       <c r="E81" s="10"/>
       <c r="F81" s="12"/>
       <c r="G81" s="3">
@@ -5203,7 +5337,9 @@
         <v>19</v>
       </c>
       <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
+      <c r="D82" s="10">
+        <v>0</v>
+      </c>
       <c r="E82" s="10"/>
       <c r="F82" s="12"/>
       <c r="G82" s="3">
@@ -5223,7 +5359,9 @@
         <v>16</v>
       </c>
       <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
+      <c r="D83" s="10">
+        <v>0</v>
+      </c>
       <c r="E83" s="10"/>
       <c r="F83" s="12"/>
       <c r="G83" s="3">
@@ -5243,7 +5381,9 @@
         <v>24</v>
       </c>
       <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
+      <c r="D84" s="10">
+        <v>0</v>
+      </c>
       <c r="E84" s="10"/>
       <c r="F84" s="12"/>
       <c r="G84" s="3">
@@ -5263,7 +5403,9 @@
         <v>26</v>
       </c>
       <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
+      <c r="D85" s="10">
+        <v>0</v>
+      </c>
       <c r="E85" s="10"/>
       <c r="F85" s="12"/>
       <c r="G85" s="3">
@@ -5283,7 +5425,9 @@
         <v>17</v>
       </c>
       <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
+      <c r="D86" s="10">
+        <v>0</v>
+      </c>
       <c r="E86" s="10"/>
       <c r="F86" s="12"/>
       <c r="G86" s="3">
@@ -5303,7 +5447,9 @@
         <v>21</v>
       </c>
       <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
+      <c r="D87" s="10">
+        <v>0</v>
+      </c>
       <c r="E87" s="10"/>
       <c r="F87" s="12"/>
       <c r="G87" s="3">
@@ -5323,7 +5469,9 @@
         <v>25</v>
       </c>
       <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
+      <c r="D88" s="10">
+        <v>0</v>
+      </c>
       <c r="E88" s="10"/>
       <c r="F88" s="12"/>
       <c r="G88" s="3">
@@ -5343,7 +5491,9 @@
         <v>23</v>
       </c>
       <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
+      <c r="D89" s="10">
+        <v>0</v>
+      </c>
       <c r="E89" s="10"/>
       <c r="F89" s="12"/>
       <c r="G89" s="3">
@@ -5373,7 +5523,9 @@
         <v>28</v>
       </c>
       <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+      <c r="D91" s="10">
+        <v>0</v>
+      </c>
       <c r="E91" s="1"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3">
@@ -5393,7 +5545,9 @@
         <v>29</v>
       </c>
       <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="D92" s="10">
+        <v>0</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3">
@@ -5413,7 +5567,9 @@
         <v>30</v>
       </c>
       <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+      <c r="D93" s="10">
+        <v>0</v>
+      </c>
       <c r="E93" s="1"/>
       <c r="F93" s="5"/>
       <c r="G93" s="3">
@@ -5433,7 +5589,9 @@
         <v>31</v>
       </c>
       <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+      <c r="D94" s="10">
+        <v>0</v>
+      </c>
       <c r="E94" s="1"/>
       <c r="F94" s="5"/>
       <c r="G94" s="3">
@@ -5453,7 +5611,9 @@
         <v>32</v>
       </c>
       <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+      <c r="D95" s="10">
+        <v>0</v>
+      </c>
       <c r="E95" s="1"/>
       <c r="F95" s="5"/>
       <c r="G95" s="3">
@@ -5473,7 +5633,9 @@
         <v>33</v>
       </c>
       <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
+      <c r="D96" s="10">
+        <v>0</v>
+      </c>
       <c r="E96" s="1"/>
       <c r="F96" s="5"/>
       <c r="G96" s="3">
@@ -5493,7 +5655,9 @@
         <v>34</v>
       </c>
       <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+      <c r="D97" s="10">
+        <v>0</v>
+      </c>
       <c r="E97" s="1"/>
       <c r="F97" s="5"/>
       <c r="G97" s="3">
@@ -5513,7 +5677,9 @@
         <v>35</v>
       </c>
       <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="D98" s="10">
+        <v>0</v>
+      </c>
       <c r="E98" s="1"/>
       <c r="F98" s="5"/>
       <c r="G98" s="3">
@@ -5525,18 +5691,27 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99" spans="1:8" ht="19.5">
+      <c r="D99" s="10"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
+    <protectedRange sqref="C1:E90 C91:C98 E91:E98 D91:D99" name="Textbooks"/>
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29" xr:uid="{0EF4E7BF-746E-4E6C-B19E-6996333D38A2}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{BCCCD43D-40B4-48EE-88C0-CCAACA27C842}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5548,7 +5723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5872,7 +6047,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1088</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -6167,7 +6344,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1088</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -6313,7 +6492,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1088</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -6397,7 +6578,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -6468,7 +6651,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -6539,7 +6724,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
@@ -6610,7 +6797,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
@@ -6681,7 +6870,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -6752,7 +6943,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -6823,7 +7016,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
@@ -6894,7 +7089,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1296</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -6979,7 +7176,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -7050,7 +7249,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -7121,7 +7322,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -7192,7 +7395,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
@@ -7263,7 +7468,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -7334,7 +7541,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
@@ -7405,7 +7614,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
@@ -7476,7 +7687,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
@@ -7547,7 +7760,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1104</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -7632,7 +7847,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5">
+        <v>0</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
@@ -7703,7 +7920,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5">
+        <v>0</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
@@ -7774,7 +7993,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5">
+        <v>0</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
@@ -7845,7 +8066,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
@@ -7916,7 +8139,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
@@ -8064,7 +8289,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
@@ -8135,7 +8362,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
@@ -8206,7 +8435,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1312</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
@@ -8291,7 +8522,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5">
+        <v>0</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
@@ -8362,7 +8595,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5">
+        <v>0</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
@@ -8433,7 +8668,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>0</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
@@ -8504,7 +8741,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5">
+        <v>0</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
@@ -8575,7 +8814,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5">
+        <v>0</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
@@ -8646,7 +8887,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5">
+        <v>0</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
@@ -8717,7 +8960,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5">
+        <v>0</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
@@ -8788,7 +9033,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5">
+        <v>0</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
@@ -8859,7 +9106,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5">
+        <v>0</v>
+      </c>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
@@ -8944,7 +9193,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5">
+        <v>0</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
@@ -9015,7 +9266,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5">
+        <v>0</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
@@ -9086,7 +9339,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>0</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -9157,7 +9412,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -9228,7 +9485,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>0</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -9299,7 +9558,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -9370,7 +9631,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>0</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -9441,7 +9704,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -9512,7 +9777,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1336</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -9583,7 +9850,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9595,7 +9862,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E63" s="12"/>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
       <c r="F63" s="10"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12">
@@ -9652,7 +9921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9664,7 +9933,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E64" s="12"/>
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
       <c r="F64" s="10"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12">
@@ -9721,7 +9992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9733,7 +10004,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E65" s="12"/>
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
       <c r="F65" s="10"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12">
@@ -9790,7 +10063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9802,7 +10075,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E66" s="12"/>
+      <c r="E66" s="12">
+        <v>0</v>
+      </c>
       <c r="F66" s="10"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12">
@@ -9859,7 +10134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9871,7 +10146,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E67" s="12"/>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
       <c r="F67" s="10"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12">
@@ -9928,7 +10205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9940,7 +10217,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E68" s="12"/>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
       <c r="F68" s="10"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12">
@@ -9997,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10009,7 +10288,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E69" s="12"/>
+      <c r="E69" s="12">
+        <v>0</v>
+      </c>
       <c r="F69" s="10"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12">
@@ -10066,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10078,7 +10359,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E70" s="12"/>
+      <c r="E70" s="12">
+        <v>0</v>
+      </c>
       <c r="F70" s="10"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
@@ -10135,7 +10418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10147,7 +10430,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E71" s="12"/>
+      <c r="E71" s="12">
+        <v>0</v>
+      </c>
       <c r="F71" s="10"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12">
@@ -10218,7 +10503,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10230,7 +10515,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E73" s="12"/>
+      <c r="E73" s="12">
+        <v>0</v>
+      </c>
       <c r="F73" s="10"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12">
@@ -10287,7 +10574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10299,7 +10586,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E74" s="12"/>
+      <c r="E74" s="12">
+        <v>0</v>
+      </c>
       <c r="F74" s="10"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12">
@@ -10356,7 +10645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10368,7 +10657,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E75" s="12"/>
+      <c r="E75" s="12">
+        <v>0</v>
+      </c>
       <c r="F75" s="10"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12">
@@ -10425,7 +10716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10437,7 +10728,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E76" s="12"/>
+      <c r="E76" s="12">
+        <v>0</v>
+      </c>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
@@ -10494,7 +10787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10506,7 +10799,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E77" s="12"/>
+      <c r="E77" s="12">
+        <v>0</v>
+      </c>
       <c r="F77" s="10"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12">
@@ -10563,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10575,7 +10870,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E78" s="12"/>
+      <c r="E78" s="12">
+        <v>0</v>
+      </c>
       <c r="F78" s="10"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
@@ -10632,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10644,7 +10941,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E79" s="12"/>
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
       <c r="F79" s="10"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
@@ -10701,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10713,7 +11012,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E80" s="12"/>
+      <c r="E80" s="12">
+        <v>0</v>
+      </c>
       <c r="F80" s="10"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
@@ -10770,7 +11071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10782,7 +11083,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E81" s="12"/>
+      <c r="E81" s="12">
+        <v>0</v>
+      </c>
       <c r="F81" s="10"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
@@ -10853,7 +11156,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10865,7 +11168,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E83" s="12"/>
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
       <c r="F83" s="10"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
@@ -10922,7 +11227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10934,7 +11239,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E84" s="12"/>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
@@ -10991,7 +11298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11003,7 +11310,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E85" s="12"/>
+      <c r="E85" s="12">
+        <v>0</v>
+      </c>
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
@@ -11060,7 +11369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11072,7 +11381,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E86" s="12"/>
+      <c r="E86" s="12">
+        <v>0</v>
+      </c>
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
@@ -11129,7 +11440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11141,7 +11452,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E87" s="12"/>
+      <c r="E87" s="12">
+        <v>0</v>
+      </c>
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
@@ -11198,7 +11511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11210,7 +11523,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E88" s="12"/>
+      <c r="E88" s="12">
+        <v>0</v>
+      </c>
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
@@ -11267,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11279,7 +11594,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E89" s="12"/>
+      <c r="E89" s="12">
+        <v>0</v>
+      </c>
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
@@ -11336,7 +11653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11348,7 +11665,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E90" s="12"/>
+      <c r="E90" s="12">
+        <v>0</v>
+      </c>
       <c r="F90" s="10"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12">
@@ -11405,7 +11724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11417,7 +11736,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E91" s="12"/>
+      <c r="E91" s="12">
+        <v>0</v>
+      </c>
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
@@ -11488,7 +11809,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11500,7 +11821,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E93" s="12"/>
+      <c r="E93" s="12">
+        <v>0</v>
+      </c>
       <c r="F93" s="10"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
@@ -11557,7 +11880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11569,7 +11892,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E94" s="12"/>
+      <c r="E94" s="12">
+        <v>0</v>
+      </c>
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
@@ -11626,7 +11951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11638,7 +11963,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E95" s="12"/>
+      <c r="E95" s="12">
+        <v>0</v>
+      </c>
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
@@ -11695,7 +12022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11707,7 +12034,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E96" s="12"/>
+      <c r="E96" s="12">
+        <v>0</v>
+      </c>
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
@@ -11764,7 +12093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11776,7 +12105,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E97" s="12"/>
+      <c r="E97" s="12">
+        <v>0</v>
+      </c>
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
@@ -11833,7 +12164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11845,7 +12176,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E98" s="12"/>
+      <c r="E98" s="12">
+        <v>0</v>
+      </c>
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
@@ -11902,7 +12235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11914,7 +12247,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E99" s="12"/>
+      <c r="E99" s="12">
+        <v>0</v>
+      </c>
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
@@ -11971,7 +12306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11983,7 +12318,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E100" s="12"/>
+      <c r="E100" s="12">
+        <v>0</v>
+      </c>
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
@@ -12040,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12052,7 +12389,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E101" s="12"/>
+      <c r="E101" s="12">
+        <v>0</v>
+      </c>
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
@@ -12123,7 +12462,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>27</v>
       </c>
@@ -12135,7 +12474,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E103" s="5"/>
+      <c r="E103" s="5">
+        <v>0</v>
+      </c>
       <c r="F103" s="1"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
@@ -12192,7 +12533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>27</v>
       </c>
@@ -12204,7 +12545,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E104" s="5"/>
+      <c r="E104" s="5">
+        <v>0</v>
+      </c>
       <c r="F104" s="1"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
@@ -12261,7 +12604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>27</v>
       </c>
@@ -12273,7 +12616,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E105" s="5"/>
+      <c r="E105" s="5">
+        <v>0</v>
+      </c>
       <c r="F105" s="1"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
@@ -12330,7 +12675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>27</v>
       </c>
@@ -12342,7 +12687,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E106" s="5"/>
+      <c r="E106" s="5">
+        <v>0</v>
+      </c>
       <c r="F106" s="1"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
@@ -12399,7 +12746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>27</v>
       </c>
@@ -12411,7 +12758,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E107" s="5"/>
+      <c r="E107" s="5">
+        <v>0</v>
+      </c>
       <c r="F107" s="1"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5">
@@ -12468,7 +12817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>27</v>
       </c>
@@ -12480,7 +12829,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E108" s="5"/>
+      <c r="E108" s="5">
+        <v>0</v>
+      </c>
       <c r="F108" s="1"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5">
@@ -12537,7 +12888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>27</v>
       </c>
@@ -12549,7 +12900,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E109" s="5"/>
+      <c r="E109" s="5">
+        <v>0</v>
+      </c>
       <c r="F109" s="1"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5">
@@ -12606,7 +12959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>27</v>
       </c>
@@ -12618,7 +12971,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E110" s="5"/>
+      <c r="E110" s="5">
+        <v>0</v>
+      </c>
       <c r="F110" s="1"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5">
@@ -13675,190 +14030,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13868,15 +14043,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 X112:X127 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F5:F12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{0290D37D-D4A4-4E13-AC77-353B05E54F94}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22479,12 +22657,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{B93B29C2-3259-4098-8843-41B491D0CA1E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
